--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2153,6 +2153,132 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127927104</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nedergårdskogen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>505760</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6576793</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anneli Sjöstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anneli Sjöstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>127927104</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>127927104</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>127927104</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>127927104</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>127927104</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>127927104</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>127927104</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2158,7 +2158,7 @@
         <v>127927104</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2284,7 +2284,7 @@
         <v>127927401</v>
       </c>
       <c r="B14" t="n">
-        <v>93002</v>
+        <v>93005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2284,7 +2284,7 @@
         <v>127927401</v>
       </c>
       <c r="B14" t="n">
-        <v>93005</v>
+        <v>93031</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2284,7 +2284,7 @@
         <v>127927401</v>
       </c>
       <c r="B14" t="n">
-        <v>93031</v>
+        <v>93032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2284,7 +2284,7 @@
         <v>127927401</v>
       </c>
       <c r="B14" t="n">
-        <v>93032</v>
+        <v>93033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2284,7 +2284,7 @@
         <v>127927401</v>
       </c>
       <c r="B14" t="n">
-        <v>93033</v>
+        <v>93035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2284,7 +2284,7 @@
         <v>127927401</v>
       </c>
       <c r="B14" t="n">
-        <v>93035</v>
+        <v>93039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2284,7 +2284,7 @@
         <v>127927401</v>
       </c>
       <c r="B14" t="n">
-        <v>93039</v>
+        <v>93052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2284,7 +2284,7 @@
         <v>127927401</v>
       </c>
       <c r="B14" t="n">
-        <v>93052</v>
+        <v>93053</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -2284,7 +2284,7 @@
         <v>127927401</v>
       </c>
       <c r="B14" t="n">
-        <v>93053</v>
+        <v>93054</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -675,49 +675,36 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109585074</v>
+        <v>109585494</v>
       </c>
       <c r="B2" t="n">
-        <v>88806</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5685</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505873.977035729</v>
+        <v>505881</v>
       </c>
       <c r="R2" t="n">
-        <v>6576829.225797311</v>
+        <v>6576766</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>växte på undersidan på låga resupinalt</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +768,27 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre barrskog på sandmark med utbrett mosstäcke och lågor av gran och tall</t>
+          <t>Äldre barrskog med mossmatta och stenblock</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Granlåga i nedbrytning, delvis övervuxen med mossa, bark kvar men inga grenar.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga i nedbrytning, delvis övervuxen med mossa, bark kvar men inga grenar.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,22 +799,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand, Barbro Fehrm Friberg</t>
+          <t>Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109585494</v>
+        <v>127927401</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,40 +817,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nedergården/gölafallet, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505880.7193843753</v>
+        <v>505938</v>
       </c>
       <c r="R3" t="n">
-        <v>6576766.473941237</v>
+        <v>6576779</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,22 +880,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-07</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,39 +904,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Äldre barrskog med mossmatta och stenblock</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Granlåga i nedbrytning, delvis övervuxen med mossa, bark kvar men inga grenar.</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga i nedbrytning, delvis övervuxen med mossa, bark kvar men inga grenar.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -960,66 +922,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109752063</v>
+        <v>109585074</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nedergårdskogen, Nrk</t>
+          <t>Nedergården/gölafallet, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505870.4345336222</v>
+        <v>505874</v>
       </c>
       <c r="R4" t="n">
-        <v>6576806.25860841</v>
+        <v>6576830</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,27 +998,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-05-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2023-05-27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Tydligt hackläte som en kulspruta, flög iväg men kom sen tillbaka och flög då förbi som för att spana in mig.</t>
+          <t>växte på undersidan på låga resupinalt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1075,8 +1017,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre barrskog på sandmark med utbrett mosstäcke och lågor av gran och tall</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1086,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand</t>
+          <t>Anneli Sjöstrand, Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1096,16 +1049,11 @@
         <v>109751997</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1149,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505904.2915828861</v>
+        <v>505904</v>
       </c>
       <c r="R5" t="n">
-        <v>6576728.750647157</v>
+        <v>6576729</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1226,62 +1174,61 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109584631</v>
+        <v>109752063</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedergårdenskogen vid stigen, Nrk</t>
+          <t>Nedergårdskogen, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505835.172685825</v>
+        <v>505870</v>
       </c>
       <c r="R6" t="n">
-        <v>6576801.101541567</v>
+        <v>6576807</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1308,22 +1255,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
+          <t>2023-06-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
+          <t>2023-06-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tydligt hackläte som en kulspruta, flög iväg men kom sen tillbaka och flög då förbi som för att spana in mig.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1332,19 +1284,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Barrskog i ett område med lågor och mossmatta vid stig</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1354,69 +1295,60 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand, Barbro Fehrm Friberg</t>
+          <t>Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109584749</v>
+        <v>109859948</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nedergårdenskogen vid stigen, Nrk</t>
+          <t>Nedergårdsskogen , Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505798.8095858297</v>
+        <v>505914</v>
       </c>
       <c r="R7" t="n">
-        <v>6576847.479315501</v>
+        <v>6576771</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1443,27 +1375,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Vissa plantor hade knoppar, övriga var i olika storlek från små plantor som var på gång till fullt utvecklade blad. Dessa var i ett stråk som sträckte sig ca 3 m och var ca 70 cm brett. Bedömt 100 plantor efter räkning.</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1472,19 +1389,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Sandbarrskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Vid lågor av tall och gran i olika stadier av nedbrytning. Mossmatta, äldre skog.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1494,69 +1400,64 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand, Barbro Fehrm Friberg</t>
+          <t>Anneli Sjöstrand, Lotta Sörman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109751777</v>
+        <v>109584631</v>
       </c>
       <c r="B8" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nedergårdskogen, Nrk</t>
+          <t>Nedergårdenskogen vid stigen, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505760.5563449501</v>
+        <v>505836</v>
       </c>
       <c r="R8" t="n">
-        <v>6576792.823203764</v>
+        <v>6576801</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1583,27 +1484,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lokal med ca 67 plantor, en hade satt knopp.</t>
+          <t>2023-05-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1616,6 +1502,16 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrskog i ett område med lågor och mossmatta vid stig</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
@@ -1624,22 +1520,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand</t>
+          <t>Anneli Sjöstrand, Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109584834</v>
+        <v>109584749</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1666,13 +1557,13 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1683,10 +1574,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505823.8739457225</v>
+        <v>505799</v>
       </c>
       <c r="R9" t="n">
-        <v>6576835.781837797</v>
+        <v>6576847</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1716,19 +1607,14 @@
           <t>2023-05-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-05-27</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vissa plantor hade knoppar, övriga var i olika storlek från små plantor som var på gång till fullt utvecklade blad. Dessa var i ett stråk som sträckte sig ca 3 m och var ca 70 cm brett. Bedömt 100 plantor efter räkning.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1748,7 +1634,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Äldre barrskog på sandmark med utbrett mosstäcke och lågor av gran och tall</t>
+          <t>Vid lågor av tall och gran i olika stadier av nedbrytning. Mossmatta, äldre skog.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1766,15 +1652,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109584883</v>
+        <v>109584834</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1801,13 +1682,13 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1818,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505819.2923867816</v>
+        <v>505824</v>
       </c>
       <c r="R10" t="n">
-        <v>6576823.528599614</v>
+        <v>6576835</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1851,24 +1732,9 @@
           <t>2023-05-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-05-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Knärötter i olika stadier från späda blad till fullt utvecklade blad där vissa satt knopp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1906,15 +1772,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109852145</v>
+        <v>109584883</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1941,14 +1802,10 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>blomknopp</t>
@@ -1958,14 +1815,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedergårdsskofem, Nrk</t>
+          <t>Nedergårdenskogen vid stigen, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505825.4520991413</v>
+        <v>505819</v>
       </c>
       <c r="R11" t="n">
-        <v>6576806.699470042</v>
+        <v>6576824</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1992,22 +1849,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Knärötter i olika stadier från späda blad till fullt utvecklade blad där vissa satt knopp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2020,6 +1872,16 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Sandbarrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre barrskog på sandmark med utbrett mosstäcke och lågor av gran och tall</t>
+        </is>
+      </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
@@ -2028,65 +1890,68 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anneli Sjöstrand, Lotta Sörman</t>
+          <t>Anneli Sjöstrand, Barbro Fehrm Friberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109859948</v>
+        <v>109852145</v>
       </c>
       <c r="B12" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Nedergårdsskogen , Nrk</t>
+          <t>Nedergårdsskofem, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505914.9599700071</v>
+        <v>505825</v>
       </c>
       <c r="R12" t="n">
-        <v>6576771.119617737</v>
+        <v>6576807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2116,27 +1981,18 @@
           <t>2023-06-06</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-06-06</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2158,7 +2014,7 @@
         <v>127927104</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2281,54 +2137,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127927401</v>
+        <v>109751777</v>
       </c>
       <c r="B14" t="n">
-        <v>93054</v>
+        <v>106244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nedergården/gölafallet, Nrk</t>
+          <t>Nedergårdskogen, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505938</v>
+        <v>505760</v>
       </c>
       <c r="R14" t="n">
-        <v>6576779</v>
+        <v>6576793</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2355,22 +2214,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:57</t>
+          <t>2023-06-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:57</t>
+          <t>2023-06-03</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Lokal med ca 67 plantor, en hade satt knopp.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2379,6 +2233,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15758-2023 artfynd.xlsx
+++ b/artfynd/A 15758-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109585494</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127927401</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109585074</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1171,6 +1191,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109751997</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1299,6 +1324,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109752063</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1404,6 +1434,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109859948</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1524,6 +1559,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109584631</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1649,6 +1689,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109584749</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1769,6 +1814,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109584834</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1894,6 +1944,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109584883</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2008,6 +2063,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109852145</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2134,6 +2194,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127927104</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2249,8 +2314,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109751777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>